--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484599_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484599_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6707</v>
+        <v>3.259</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9373</v>
+        <v>3.5255</v>
       </c>
       <c r="F2" t="n">
         <v>-0.2666</v>
@@ -610,10 +610,10 @@
         <v>1.6493</v>
       </c>
       <c r="S2" t="n">
-        <v>1.172</v>
+        <v>0.7602</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4178</v>
+        <v>0.0061</v>
       </c>
       <c r="U2" t="n">
         <v>0.7541</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3631</v>
+        <v>0.9013</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9397</v>
+        <v>0.6512</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4234</v>
+        <v>0.25</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2807</v>
@@ -688,13 +688,13 @@
         <v>0.5498</v>
       </c>
       <c r="S3" t="n">
-        <v>1.094</v>
+        <v>0.6322</v>
       </c>
       <c r="T3" t="n">
-        <v>0.457</v>
+        <v>0.1686</v>
       </c>
       <c r="U3" t="n">
-        <v>0.637</v>
+        <v>0.4636</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1831</v>
+        <v>-0.406</v>
       </c>
       <c r="E4" t="n">
         <v>-0.5038</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3207</v>
+        <v>0.0978</v>
       </c>
       <c r="G4" t="n">
         <v>-0.1634</v>
@@ -766,13 +766,13 @@
         <v>0.3665</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5301</v>
+        <v>0.3071</v>
       </c>
       <c r="T4" t="n">
         <v>0.2919</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2382</v>
+        <v>0.0153</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BALAGUER BARBA</t>
+          <t>J. MARIA VENTURA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2458</v>
+        <v>-0.453</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4899</v>
+        <v>0.5827</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7358</v>
+        <v>-1.0358</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3733</v>
+        <v>-0.1883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0018</v>
+        <v>-1.7303</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.3751</v>
+        <v>1.5419</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3902</v>
+        <v>0.72</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7987</v>
+        <v>-0.5977</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1889</v>
+        <v>1.3177</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9831</v>
+        <v>-0.9083</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7968</v>
+        <v>-1.1326</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1863</v>
+        <v>0.2243</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2478</v>
+        <v>-0.5317</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5294</v>
+        <v>0.1456</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2816</v>
+        <v>-0.6772</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8796</v>
+        <v>0.6335</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6127</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARIA VENTURA</t>
+          <t>P. BALAGUER BARBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9367</v>
+        <v>-0.462</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1981</v>
+        <v>-0.073</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1349</v>
+        <v>-0.3889</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1883</v>
+        <v>-2.3733</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7303</v>
+        <v>0.0018</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5419</v>
+        <v>-2.3751</v>
       </c>
       <c r="J6" t="n">
-        <v>0.72</v>
+        <v>-0.3902</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5977</v>
+        <v>0.7987</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3177</v>
+        <v>-1.1889</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9083</v>
+        <v>-1.9831</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1326</v>
+        <v>-0.7968</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2243</v>
+        <v>-1.1863</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0154</v>
+        <v>0.0317</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2391</v>
+        <v>-0.0335</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7763</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6335</v>
+        <v>1.8796</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6335</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.6127</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4362</v>
+        <v>-0.9907</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.3319</v>
+        <v>-2.0845</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8956</v>
+        <v>1.0938</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9085</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2608</v>
+        <v>-0.8152</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4955</v>
+        <v>-0.2481</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7653</v>
+        <v>-0.5671</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5325</v>
+        <v>-1.4363</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0153</v>
+        <v>0.0809</v>
       </c>
       <c r="F8" t="n">
         <v>-1.5172</v>
@@ -1078,10 +1078,10 @@
         <v>0.1833</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0369</v>
+        <v>0.0592</v>
       </c>
       <c r="U8" t="n">
         <v>-0.1282</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2179</v>
+        <v>-1.9512</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7962</v>
+        <v>-0.6039</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4217</v>
+        <v>-1.3473</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3302</v>
@@ -1156,13 +1156,13 @@
         <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4271</v>
+        <v>-0.1604</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2069</v>
+        <v>-0.1325</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6439</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. LARA BARRACHINA</t>
+          <t>J. TORRES HERNANDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1096</v>
+        <v>-2.4145</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8774</v>
+        <v>0.48</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2322</v>
+        <v>-2.8945</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.35</v>
+        <v>-3.4895</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3559</v>
+        <v>-0.3486</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9941</v>
+        <v>-3.1409</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2043</v>
+        <v>-0.5506</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6292</v>
+        <v>0.6345</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8335</v>
+        <v>-1.1851</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5543</v>
+        <v>-2.9389</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7267</v>
+        <v>-0.9831</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8276</v>
+        <v>-1.9558</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1078</v>
+        <v>0.2425</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1862</v>
+        <v>-0.2364</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0785</v>
+        <v>0.4789</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5681</v>
+        <v>-0.6335</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0208</v>
+        <v>1.267</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5889</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. TORRES HERNANDO</t>
+          <t>M. LARA BARRACHINA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.445</v>
+        <v>-3.3131</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5506</v>
+        <v>-0.8084</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.8945</v>
+        <v>-2.5047</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4895</v>
+        <v>-2.35</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3486</v>
+        <v>-1.3559</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1409</v>
+        <v>-0.9941</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5506</v>
+        <v>0.2043</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6345</v>
+        <v>-0.6292</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.1851</v>
+        <v>0.8335</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9389</v>
+        <v>-2.5543</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9831</v>
+        <v>-0.7267</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9558</v>
+        <v>-1.8276</v>
       </c>
       <c r="P11" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7881</v>
+        <v>-0.3113</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2669</v>
+        <v>-0.1172</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4789</v>
+        <v>-0.194</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6335</v>
+        <v>-1.5681</v>
       </c>
       <c r="W11" t="n">
-        <v>1.267</v>
+        <v>0.0208</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.9005</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8533</v>
+        <v>-4.1418</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1713</v>
+        <v>-3.4597</v>
       </c>
       <c r="F12" t="n">
         <v>-0.6821</v>
@@ -1390,10 +1390,10 @@
         <v>0.733</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0807</v>
+        <v>0.7922</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7127</v>
+        <v>0.4242</v>
       </c>
       <c r="U12" t="n">
         <v>0.368</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.3708</v>
+        <v>-7.0629</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5861</v>
+        <v>-2.2286</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.7847</v>
+        <v>-4.8343</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9267</v>
@@ -1468,13 +1468,13 @@
         <v>1.8326</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4546</v>
+        <v>-0.1467</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4427</v>
+        <v>-0.0852</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0119</v>
+        <v>-0.0615</v>
       </c>
       <c r="V13" t="n">
         <v>-3.157</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-19.2971</v>
+        <v>-18.4712</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.267600000000001</v>
+        <v>-4.4416</v>
       </c>
       <c r="F14" t="n">
-        <v>-14.03</v>
+        <v>-14.0298</v>
       </c>
       <c r="G14" t="n">
         <v>-19.1639</v>
@@ -1546,22 +1546,22 @@
         <v>10.9956</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09440000000000026</v>
+        <v>0.7315999999999998</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4787</v>
+        <v>0.3473</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3845000000000001</v>
+        <v>0.3845999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-0.9554999999999998</v>
       </c>
       <c r="W14" t="n">
-        <v>6.698499999999999</v>
+        <v>6.6985</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.6539</v>
+        <v>-7.653899999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6751</v>
+        <v>4.7883</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7087</v>
+        <v>5.1894</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0335</v>
+        <v>-0.4012</v>
       </c>
       <c r="G15" t="n">
         <v>3.6987</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.1176</v>
+        <v>-0.0045</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8627</v>
+        <v>-0.382</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2549</v>
+        <v>0.3774</v>
       </c>
       <c r="V15" t="n">
         <v>1.2774</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3576</v>
+        <v>3.8049</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0622</v>
+        <v>2.1583</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2954</v>
+        <v>1.6466</v>
       </c>
       <c r="G16" t="n">
         <v>2.767</v>
@@ -1702,13 +1702,13 @@
         <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4931</v>
+        <v>-0.0458</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3673</v>
+        <v>-0.2711</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1259</v>
+        <v>0.2253</v>
       </c>
       <c r="V16" t="n">
         <v>1.267</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PEÑA</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1507</v>
+        <v>3.347</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1507</v>
+        <v>1.4531</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.8939</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1507</v>
+        <v>3.7306</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6502</v>
+        <v>0.9514</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5005</v>
+        <v>2.7791</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1507</v>
+        <v>1.9862</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6502</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5005</v>
+        <v>1.401</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.7443</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.3662</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.3781</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4661</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.2608</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5332</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2724</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0609</v>
+        <v>3.291</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6159</v>
+        <v>0.8082</v>
       </c>
       <c r="F18" t="n">
-        <v>2.445</v>
+        <v>2.4828</v>
       </c>
       <c r="G18" t="n">
         <v>0.6752</v>
@@ -1858,13 +1858,13 @@
         <v>1.4661</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0646</v>
+        <v>0.1655</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8092</v>
+        <v>-0.6169</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7446</v>
+        <v>0.7824</v>
       </c>
       <c r="V18" t="n">
         <v>1.9005</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>D. ARIJA DE LA PEÑA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.7307</v>
+        <v>3.1507</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0684</v>
+        <v>3.1507</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6623</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7306</v>
+        <v>3.1507</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9514</v>
+        <v>0.6502</v>
       </c>
       <c r="I19" t="n">
-        <v>2.7791</v>
+        <v>2.5005</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9862</v>
+        <v>3.1507</v>
       </c>
       <c r="K19" t="n">
-        <v>0.5852000000000001</v>
+        <v>0.6502</v>
       </c>
       <c r="L19" t="n">
-        <v>1.401</v>
+        <v>2.5005</v>
       </c>
       <c r="M19" t="n">
-        <v>1.7443</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3662</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3781</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.877</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9177999999999999</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. NEBOT GARCIA</t>
+          <t>P. ARISTA CALLAU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.5646</v>
+        <v>2.0325</v>
       </c>
       <c r="E20" t="n">
-        <v>2.46</v>
+        <v>2.4262</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1046</v>
+        <v>-0.3937</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6943</v>
+        <v>3.7221</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5822</v>
+        <v>1.0616</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8879</v>
+        <v>2.6605</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7753</v>
+        <v>3.9441</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3747</v>
+        <v>1.0588</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5994</v>
+        <v>2.8854</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.081</v>
+        <v>-0.222</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2075</v>
+        <v>0.0029</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2885</v>
+        <v>-0.2249</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1833</v>
+        <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>1.9986</v>
+        <v>-0.0824</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9962</v>
+        <v>-0.3005</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0023</v>
+        <v>0.2181</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>-2.5235</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>-0.3011</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. DIAGNE</t>
+          <t>M. NEBOT GARCIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6602</v>
+        <v>1.5142</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5242</v>
+        <v>1.3062</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1843</v>
+        <v>0.208</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2418</v>
+        <v>0.6943</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3827</v>
+        <v>1.5822</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1408</v>
+        <v>-0.8879</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3008</v>
+        <v>0.7753</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5766</v>
+        <v>1.3747</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2758</v>
+        <v>-0.5994</v>
       </c>
       <c r="M21" t="n">
-        <v>0.059</v>
+        <v>-0.081</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.806</v>
+        <v>0.2075</v>
       </c>
       <c r="O21" t="n">
-        <v>0.865</v>
+        <v>-0.2885</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5498</v>
+        <v>0.1833</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>1.9961</v>
+        <v>0.9482</v>
       </c>
       <c r="T21" t="n">
-        <v>1.316</v>
+        <v>0.8424</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6801</v>
+        <v>0.1058</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6439</v>
+        <v>-0.3115</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6231</v>
+        <v>-0.3115</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ARISTA CALLAU</t>
+          <t>C. CAMAHORT TORRES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7605</v>
+        <v>0.6742</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1378</v>
+        <v>-0.0881</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3773</v>
+        <v>0.7623</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7221</v>
+        <v>0.0349</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0616</v>
+        <v>0.9228</v>
       </c>
       <c r="I22" t="n">
-        <v>2.6605</v>
+        <v>-0.8879</v>
       </c>
       <c r="J22" t="n">
-        <v>3.9441</v>
+        <v>0.1159</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0588</v>
+        <v>0.7153</v>
       </c>
       <c r="L22" t="n">
-        <v>2.8854</v>
+        <v>-0.5994</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.222</v>
+        <v>-0.081</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0029</v>
+        <v>0.2075</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2249</v>
+        <v>-0.2885</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8326</v>
+        <v>0.1833</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3544</v>
+        <v>0.3986</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.589</v>
+        <v>0.3616</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7654</v>
+        <v>0.0369</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.5235</v>
+        <v>1.89</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3011</v>
+        <v>1.267</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.2224</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C. CAMAHORT TORRES</t>
+          <t>E. DIAGNE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1584</v>
+        <v>0.292</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3765</v>
+        <v>-1.678</v>
       </c>
       <c r="F23" t="n">
-        <v>0.535</v>
+        <v>1.97</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0349</v>
+        <v>-0.2418</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9228</v>
+        <v>-1.3827</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8879</v>
+        <v>1.1408</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1159</v>
+        <v>-0.3008</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7153</v>
+        <v>-0.5766</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5994</v>
+        <v>0.2758</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.081</v>
+        <v>0.059</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2075</v>
+        <v>-0.806</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2885</v>
+        <v>0.865</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1172</v>
+        <v>0.628</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0732</v>
+        <v>0.1622</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1903</v>
+        <v>0.4658</v>
       </c>
       <c r="V23" t="n">
-        <v>1.89</v>
+        <v>-0.6439</v>
       </c>
       <c r="W23" t="n">
-        <v>1.267</v>
+        <v>-0.6231</v>
       </c>
       <c r="X23" t="n">
-        <v>0.6231</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2429</v>
+        <v>0.1315</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3923</v>
+        <v>-0.2</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1494</v>
+        <v>0.3315</v>
       </c>
       <c r="G24" t="n">
         <v>2.306</v>
@@ -2326,13 +2326,13 @@
         <v>1.2828</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4885</v>
+        <v>-0.1141</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.5249</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2287</v>
+        <v>0.4108</v>
       </c>
       <c r="V24" t="n">
         <v>0.3219</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4881</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3258</v>
+        <v>-0.0373</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1624</v>
+        <v>-0.0589</v>
       </c>
       <c r="G25" t="n">
         <v>-0.1051</v>
@@ -2404,13 +2404,13 @@
         <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.0165</v>
+        <v>0.3754</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1471</v>
+        <v>0.1414</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1305</v>
+        <v>0.234</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.0906</v>
+        <v>-1.0688</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5551</v>
+        <v>-0.4589</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5355</v>
+        <v>-0.6099</v>
       </c>
       <c r="G26" t="n">
         <v>-1.2688</v>
@@ -2482,13 +2482,13 @@
         <v>0.1833</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6284</v>
+        <v>0.6503</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6403</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0119</v>
+        <v>-0.0862</v>
       </c>
       <c r="V26" t="n">
         <v>-0.6335</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>19.2971</v>
+        <v>21.8613</v>
       </c>
       <c r="E27" t="n">
         <v>14.0298</v>
       </c>
       <c r="F27" t="n">
-        <v>5.267300000000001</v>
+        <v>7.8314</v>
       </c>
       <c r="G27" t="n">
         <v>19.1638</v>
@@ -2539,7 +2539,7 @@
         <v>10.3802</v>
       </c>
       <c r="L27" t="n">
-        <v>7.375500000000002</v>
+        <v>7.375500000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.408</v>
@@ -2551,7 +2551,7 @@
         <v>3.3628</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.9161000000000001</v>
+        <v>-0.9161000000000004</v>
       </c>
       <c r="Q27" t="n">
         <v>-10.9955</v>
@@ -2560,16 +2560,16 @@
         <v>10.0794</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09419999999999984</v>
+        <v>2.6584</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.3845999999999999</v>
+        <v>-0.3846000000000002</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4786000000000001</v>
+        <v>3.0427</v>
       </c>
       <c r="V27" t="n">
-        <v>0.9555000000000005</v>
+        <v>0.9555000000000002</v>
       </c>
       <c r="W27" t="n">
         <v>7.6541</v>
